--- a/data/trans_bre/P1426-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1426-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,23</t>
+          <t>-1,47; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,13</t>
+          <t>-2,35; 3,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,85</t>
+          <t>-1,84; 1,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,33; 542,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,84; 259,11</t>
+          <t>-63,83; 266,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 212,6</t>
+          <t>-62,02; 180,37</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-13,93%</t>
+          <t>-16,31%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,95</t>
+          <t>0,2; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,93</t>
+          <t>-0,41; 1,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,2</t>
+          <t>-2,19; 1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,64; —</t>
+          <t>-30,34; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,99; —</t>
+          <t>-100,0; 1086,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 114,11</t>
+          <t>-63,61; 94,72</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,86</t>
+          <t>-2,56; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,01</t>
+          <t>-0,72; 2,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -0,26</t>
+          <t>-7,14; -0,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-90,97; 376,45</t>
+          <t>-87,25; 293,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,58; -1,88</t>
+          <t>-61,4; -6,08</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,75</t>
+          <t>-0,88; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,64</t>
+          <t>-3,12; 0,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,11</t>
+          <t>-0,85; 3,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,71; —</t>
+          <t>-96,83; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 160,26</t>
+          <t>-100,0; 196,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,48; 101,39</t>
+          <t>-24,24; 174,48</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,15</t>
+          <t>-1,8; 6,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 6,11</t>
+          <t>-0,43; 6,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 3,83</t>
+          <t>-2,86; 4,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 319,51</t>
+          <t>-43,02; 341,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,16; —</t>
+          <t>-68,99; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 74,11</t>
+          <t>-31,54; 82,45</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,81%</t>
+          <t>-9,91%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,86</t>
+          <t>-4,16; 0,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,6</t>
+          <t>-1,49; 3,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 2,72</t>
+          <t>-5,48; 2,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-91,55; 77,48</t>
+          <t>-89,02; 101,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 534,46</t>
+          <t>-61,54; 541,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 23,18</t>
+          <t>-34,13; 27,38</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,47%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,54</t>
+          <t>-2,5; 0,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,35</t>
+          <t>0,28; 4,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,37</t>
+          <t>-1,35; 3,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-73,83; 40,55</t>
+          <t>-75,14; 46,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,44; 328,25</t>
+          <t>3,24; 313,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 50,26</t>
+          <t>-19,57; 79,81</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,35</t>
+          <t>-0,43; 1,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,35</t>
+          <t>-1,48; 0,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,37</t>
+          <t>-0,71; 1,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 864,64</t>
+          <t>-60,82; 894,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-84,76; 86,92</t>
+          <t>-85,44; 90,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 273,64</t>
+          <t>-29,56; 117,18</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,98</t>
+          <t>-0,4; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,2</t>
+          <t>-0,03; 1,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,08</t>
+          <t>-0,84; 0,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 78,93</t>
+          <t>-21,86; 79,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 102,25</t>
+          <t>-0,86; 113,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 28,85</t>
+          <t>-16,28; 18,02</t>
         </is>
       </c>
     </row>
